--- a/stem/code/DUAL-BARCODE-SCANNING-SYSTEM-3.xlsx
+++ b/stem/code/DUAL-BARCODE-SCANNING-SYSTEM-3.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="STUDENT DATABASE" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +11,7 @@
     <sheet name="TRANSACTION LOG" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -52,7 +51,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -861,19 +860,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Borrowed</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-02-27 04:40:20</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -918,6 +909,8 @@
           <t>Available</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -952,8 +945,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="12" bestFit="1" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1013,10 +1010,8 @@
           <t>T000001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>136515140138</t>
-        </is>
+      <c r="B2" t="n">
+        <v>136515140138</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1033,10 +1028,8 @@
           <t>lanze.anderson@gmail.com</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>9789716554601</t>
-        </is>
+      <c r="F2" t="n">
+        <v>9789716554601</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1066,6 +1059,583 @@
           <t>2026-03-02</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T000002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>136515140138</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LANZE ANDERSON C. LOZANO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12-STEM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lanze.anderson@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9789716554601</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Math Builders</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>return</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1772290078.73085</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-02-28 22:47:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T000003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>136515140138</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LANZE ANDERSON C. LOZANO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12-STEM</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lanze.anderson@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9789719990802</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Edukasyon Sa Pagpapakatao</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>borrow</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1772290119.88177</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-02-28 22:48:39</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T000004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>136515140138</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LANZE ANDERSON C. LOZANO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12-STEM</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lanze.anderson@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9789719990802</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Edukasyon Sa Pagpapakatao</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>borrow</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1772290201.586295</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-02-28 22:50:01</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T000005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>136515140138</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LANZE ANDERSON C. LOZANO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>12-STEM</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lanze.anderson@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9789719990802</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Edukasyon Sa Pagpapakatao</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>return</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1772290240.426476</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-02-28 22:50:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>136515140138</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LANZE ANDERSON C. LOZANO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>12-STEM</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>lanze.anderson@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9786214120178</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Skill book in Mathematics</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>borrow</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1772300560.301333</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-03-01 01:42:40</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T000007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>136515140138</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LANZE ANDERSON C. LOZANO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12-STEM</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>lanze.anderson@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>9789716554601</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Math Builders</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>borrow</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1772300870.301406</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-03-01 01:47:50</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T000008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>136515140138</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LANZE ANDERSON C. LOZANO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>12-STEM</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>lanze.anderson@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9786214120178</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Skill book in Mathematics</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>return</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1772638629.550409</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-03-04 23:37:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T000009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>136515140138</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LANZE ANDERSON C. LOZANO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>12-STEM</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>lanze.anderson@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9786214120178</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Skill book in Mathematics</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>borrow</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1772639127.117135</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-03-04 23:45:27</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T000010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>136515140138</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LANZE ANDERSON C. LOZANO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>12-STEM</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>lanze.anderson@gmail.com</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9786214120178</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Skill book in Mathematics</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>return</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1772641198.899884</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-03-05 00:19:58</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T000011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>136515140138</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LANZE ANDERSON C. LOZANO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>12-STEM</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>lanze.anderson@gmail.com</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9789716554601</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Math Builders</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>return</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1772641497.747812</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-03-05 00:24:57</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
